--- a/publication_tables/supplementary/S1_elasticity_assignment.xlsx
+++ b/publication_tables/supplementary/S1_elasticity_assignment.xlsx
@@ -481,25 +481,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD: pdr=5.05; wht=4.45; gro=1.3; v_f=1.85; osd=2.45; c_b=2.7; pfb=2.5; ocr=3.25; ctl=2; oap=1.3; rmk=3.65; wol=6.45. Equal-weight arithmetic mean, rounded to 4 decimal places. This benchmark assumption uses equal weights because subsector trade weights are unavailable; the aggregate elasticity is a mapped proxy rather than an estimate for Türkiye. The crop–livestock production block proxies A01 support and hunting activities.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD: pdr=5.05; wht=4.45; gro=1.3; v_f=1.85; osd=2.45; c_b=2.7; pfb=2.5; ocr=3.25; ctl=2; oap=1.3; rmk=3.65; wol=6.45. Eşit ağırlıklı aritmetik ortalama, 4 ondalığa yuvarlandı. Alt sektör ticaret ağırlıkları bulunmadığından seçilmiş başlangıç varsayımıdır; Türkiye için tahmin edilmiş toplam sektör esnekliği değildir. A01’in destek/avcılık faaliyetleri için bitkisel–hayvansal üretim bloğu vekil alınmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for agriculture, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Tarım grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, pdr, wht, gro, v_f, osd, c_b, pfb, ocr, ctl, oap, rmk, wol. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest. The common value of the crop–livestock production components is used.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, pdr, wht, gro, v_f, osd, c_b, pfb, ocr, ctl, oap, rmk, wol. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır. Bitkisel–hayvansal üretim bileşenlerinin ortak değeri kullanılır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -525,25 +525,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, frs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, frs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for agriculture, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Tarım grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, frs. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, frs. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -569,25 +569,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, fsh. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, fsh. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for agriculture, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Tarım grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, fsh. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, fsh. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -613,23 +613,23 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD: coa=3.05; oil=5.2; gas=17.2; oxt=0.9. Equal-weight arithmetic mean, rounded to 4 decimal places. This benchmark assumption uses equal weights because subsector trade weights are unavailable; the aggregate elasticity is a mapped proxy rather than an estimate for Türkiye.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD: coa=3.05; oil=5.2; gas=17.2; oxt=0.9. Eşit ağırlıklı aritmetik ortalama, 4 ondalığa yuvarlandı. Alt sektör ticaret ağırlıkları bulunmadığından seçilmiş başlangıç varsayımıdır; Türkiye için tahmin edilmiş toplam sektör esnekliği değildir.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for mining and quarrying. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Madencilik ve taş ocakçılığı için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -656,23 +656,23 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD: cmt=3.85; omt=4.4; vol=3.3; mil=3.65; pcr=2.6; sgr=2.7; ofd=2; b_t=1.15. Equal-weight arithmetic mean, rounded to 4 decimal places. This benchmark assumption uses equal weights because subsector trade weights are unavailable; the aggregate elasticity is a mapped proxy rather than an estimate for Türkiye.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD: cmt=3.85; omt=4.4; vol=3.3; mil=3.65; pcr=2.6; sgr=2.7; ofd=2; b_t=1.15. Eşit ağırlıklı aritmetik ortalama, 4 ondalığa yuvarlandı. Alt sektör ticaret ağırlıkları bulunmadığından seçilmiş başlangıç varsayımıdır; Türkiye için tahmin edilmiş toplam sektör esnekliği değildir.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -699,23 +699,23 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD: tex=3.75; wap=3.7; lea=4.05. Equal-weight arithmetic mean, rounded to 4 decimal places. This benchmark assumption uses equal weights because subsector trade weights are unavailable; the aggregate elasticity is a mapped proxy rather than an estimate for Türkiye.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD: tex=3.75; wap=3.7; lea=4.05. Eşit ağırlıklı aritmetik ortalama, 4 ondalığa yuvarlandı. Alt sektör ticaret ağırlıkları bulunmadığından seçilmiş başlangıç varsayımıdır; Türkiye için tahmin edilmiş toplam sektör esnekliği değildir.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -742,23 +742,23 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, lum. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, lum. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -785,23 +785,23 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ppp. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ppp. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -828,23 +828,23 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ppp. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ppp. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -871,23 +871,23 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, p_c. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, p_c. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -914,23 +914,23 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, chm. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, chm. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -957,23 +957,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, bph. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, bph. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1000,23 +1000,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, rpp. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, rpp. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1043,23 +1043,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, nmm. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, nmm. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1086,23 +1086,23 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD: i_s=2.95; nfm=4.2. Equal-weight arithmetic mean, rounded to 4 decimal places. This benchmark assumption uses equal weights because subsector trade weights are unavailable; the aggregate elasticity is a mapped proxy rather than an estimate for Türkiye.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD: i_s=2.95; nfm=4.2. Eşit ağırlıklı aritmetik ortalama, 4 ondalığa yuvarlandı. Alt sektör ticaret ağırlıkları bulunmadığından seçilmiş başlangıç varsayımıdır; Türkiye için tahmin edilmiş toplam sektör esnekliği değildir.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1129,23 +1129,23 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, fmp. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, fmp. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1172,23 +1172,23 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ele. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ele. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1215,23 +1215,23 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, eeq. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, eeq. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1258,23 +1258,23 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ome. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ome. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1301,23 +1301,23 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, mvh. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, mvh. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1344,23 +1344,23 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, otn. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, otn. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1387,23 +1387,23 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, omf. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, omf. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1430,23 +1430,23 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, omf. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, omf. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for manufacturing. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İmalat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1473,25 +1473,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ely, gdt: all components have the same value. Their common value is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ely, gdt: tüm bileşenlerde aynı değer. Ortak değer atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, ely, gdt. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, ely, gdt. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -1517,25 +1517,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, wtr. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, wtr. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, wtr. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, wtr. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -1561,25 +1561,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, wtr. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, wtr. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, wtr. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, wtr. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -1605,23 +1605,23 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, cns. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, cns. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for industry, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Sanayi grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for construction. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+İnşaat için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1648,23 +1648,23 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, trd. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, trd. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for wholesale and retail trade and motor-vehicle repair. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Toptan/perakende ticaret; motorlu taşıt onarımı için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1691,23 +1691,23 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, trd. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, trd. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for wholesale and retail trade and motor-vehicle repair. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Toptan/perakende ticaret; motorlu taşıt onarımı için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1734,23 +1734,23 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, trd. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, trd. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for wholesale and retail trade and motor-vehicle repair. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Toptan/perakende ticaret; motorlu taşıt onarımı için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1777,23 +1777,23 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, otp. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, otp. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for transportation and storage. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Ulaştırma ve depolama için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1820,23 +1820,23 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, wtp. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, wtp. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for transportation and storage. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Ulaştırma ve depolama için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1863,23 +1863,23 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, atp. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, atp. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for transportation and storage. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Ulaştırma ve depolama için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1906,23 +1906,23 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, whs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, whs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for transportation and storage. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Ulaştırma ve depolama için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1949,23 +1949,23 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, cmn. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, cmn. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for transportation and storage. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Ulaştırma ve depolama için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -1992,25 +1992,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, afs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, afs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, afs. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, afs. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2036,23 +2036,23 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, cmn. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, cmn. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for information and communication. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Bilgi ve iletişim için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -2079,23 +2079,23 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, cmn. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, cmn. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for information and communication. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Bilgi ve iletişim için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -2122,23 +2122,23 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, cmn. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, cmn. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for information and communication. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Bilgi ve iletişim için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -2165,23 +2165,23 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, cmn. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, cmn. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Kılıç and Yılmaz (2018), ICE-TEA conference paper, pp. 598–599. Türkiye, 2003–2015.
-Preliminary labour–capital CES estimate for information and communication. The broad-sector value reported in the paper is transferred to this subsector.
+          <t>Kılıç ve Yılmaz (2018), ICE-TEA bildirisi, s. 598–599. Türkiye, 2003–2015.
+Bilgi ve iletişim için emek–sermaye CES ön tahmini. Bildirideki geniş sektör değeri bu alt sektöre aktarılmıştır.
 https://www.tek.org.tr/pdf/258_2412023_150743.pdf</t>
         </is>
       </c>
@@ -2208,25 +2208,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ofi. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ofi. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, ofi. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, ofi. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2252,25 +2252,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ins. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ins. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, ins. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, ins. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2296,25 +2296,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ofi, ins: all components have the same value. Their common value is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ofi, ins: tüm bileşenlerde aynı değer. Ortak değer atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, ofi, ins. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, ofi, ins. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2340,25 +2340,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, rsa. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, rsa. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, rsa. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, rsa. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2384,25 +2384,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, dwe. The domestic–import substitution value of the corresponding GTAP sector is assigned. Benchmark imports are zero; this parameter is inactive in the current model.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, dwe. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı. Başlangıç ithalatı sıfırdır; mevcut modelde bu parametre etkin değildir.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used. Benchmark exports are zero; this parameter is inactive in the current model.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır. Başlangıç ihracatı sıfırdır; mevcut modelde bu parametre etkin değildir.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, dwe. Single-factor sector: capital only. This positive value is assigned for reporting; factor substitution is inactive in the current model.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, dwe. Tek faktörlü sektör: yalnız sermaye. Bu pozitif değer raporlama için atanmıştır; mevcut modelde faktör ikamesi etkin değildir.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2428,25 +2428,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, obs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, obs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, obs. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, obs. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2472,25 +2472,25 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, obs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, obs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, obs. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, obs. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2516,25 +2516,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, obs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, obs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, obs. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, obs. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2560,25 +2560,25 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, obs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, obs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, obs. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, obs. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2604,25 +2604,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, obs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, obs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, obs. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, obs. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2648,25 +2648,25 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, obs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, obs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, obs. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, obs. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2692,25 +2692,25 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, obs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, obs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, obs. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, obs. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2736,25 +2736,25 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, obs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, obs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, obs. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, obs. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2780,25 +2780,25 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, obs. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, obs. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, obs. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, obs. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2824,25 +2824,25 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, osg. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, osg. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, osg. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, osg. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2868,25 +2868,25 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, edu. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, edu. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, edu. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, edu. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2912,25 +2912,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, hht. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, hht. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, hht. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, hht. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -2956,25 +2956,25 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, hht. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, hht. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, hht. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, hht. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -3000,25 +3000,25 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ros. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ros. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, ros. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, ros. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -3044,25 +3044,25 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ros. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ros. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, ros. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, ros. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -3088,25 +3088,25 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ros. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ros. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, ros. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, ros. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ros. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ros. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, ros. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, ros. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -3176,25 +3176,25 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ros. The domestic–import substitution value of the corresponding GTAP sector is assigned.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ros. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, ros. In the absence of a matched sector estimate for Türkiye, GTAP primary-factor substitution is used as a proxy in the two-factor labour–capital nest.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, ros. Türkiye için eşleşen sektör tahmini bulunmadığından GTAP birincil faktör ikamesi, iki faktörlü emek–sermaye yuvasına vekil parametre olarak aktarılmıştır.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -3220,25 +3220,25 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBD, ros. The domestic–import substitution value of the corresponding GTAP sector is assigned. Benchmark imports are zero; this parameter is inactive in the current model.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBD, ros. İlgili GTAP sektörünün yerli–ithal ikame değeri atandı. Başlangıç ithalatı sıfırdır; mevcut modelde bu parametre etkin değildir.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>İnce (2026), Economies, 14, 440, Appendix B, Table A2.
-Exogenous CET assumption for services, assigned uniformly to sectors in the group. The positive-psi definition of transformation between exports and domestic sales is used. Benchmark exports are zero; this parameter is inactive in the current model.
+          <t>İnce (2026), Economies, 14, 440, Ek B, Tablo A2.
+Hizmetler grubu için dışsal CET varsayımı; aynı gruptaki sektörlere ortak atanır. İhracat–yurt içi satış dönüşümünün pozitif psi tanımı kullanılır. Başlangıç ihracatı sıfırdır; mevcut modelde bu parametre etkin değildir.
 https://doi.org/10.3390/economies14100440</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Hertel and van der Mensbrugghe (2024), GTAP 11, Table 16.2.
-ESUBVA, ros. Single-factor sector: labour only. This positive value is assigned for reporting; factor substitution is inactive in the current model.
-https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
-Sector concordance: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
+          <t>Hertel ve van der Mensbrugghe (2024), GTAP 11, Tablo 16.2.
+ESUBVA, ros. Tek faktörlü sektör: yalnız emek. Bu pozitif değer raporlama için atanmıştır; mevcut modelde faktör ikamesi etkin değildir.
+https://gtap.agecon.purdue.edu/resources/res_display.asp?RecordID=7127
+Sektör köprüsü: https://www.gtap.agecon.purdue.edu/databases/contribute/concordinfo.asp</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>datas/SAM_2023_64_sectors_5_households.xlsx: Accounts</t>
+          <t>datas/SHM_2023_64_sektor_5_hanehalki.xlsx: Hesaplar</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>../4_cge_model/codes/cge_model.py: load_elasticities()</t>
+          <t>../4_CGE_model/codes/cge_model.py: load_elasticities()</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>../4_cge_model/codes/cge_model.py: load_elasticities()</t>
+          <t>../4_CGE_model/codes/cge_model.py: load_elasticities()</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>../4_cge_model/codes/cge_model.py: load_elasticities()</t>
+          <t>../4_CGE_model/codes/cge_model.py: load_elasticities()</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>../4_cge_model/codes/cge_model.py: load_elasticities()</t>
+          <t>../4_CGE_model/codes/cge_model.py: load_elasticities()</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>../4_cge_model/codes/cge_model.py: load_elasticities()</t>
+          <t>../4_CGE_model/codes/cge_model.py: load_elasticities()</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>../4_cge_model/codes/cge_model.py: load_elasticities()</t>
+          <t>../4_CGE_model/codes/cge_model.py: load_elasticities()</t>
         </is>
       </c>
     </row>
@@ -3540,11 +3540,10 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>../4_cge_model/codes/cge_model.py: load_elasticities()</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>../4_CGE_model/codes/cge_model.py: load_elasticities()</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
